--- a/samples/수주취합/고객사D_발주서.xlsx
+++ b/samples/수주취합/고객사D_발주서.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="27">
   <si>
     <t/>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>발주수량</t>
+  </si>
+  <si>
+    <t>단가</t>
+  </si>
+  <si>
+    <t>금액</t>
   </si>
   <si>
     <t>비고</t>
@@ -1809,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
@@ -1818,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R15" t="s">
         <v>0</v>
@@ -1836,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X15" t="s">
         <v>0</v>
@@ -1865,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>0</v>
@@ -1877,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
@@ -1886,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
         <v>0</v>
@@ -1900,8 +1906,8 @@
       <c r="M16" t="s">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>0</v>
+      <c r="N16">
+        <v>2800</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
@@ -1909,8 +1915,8 @@
       <c r="P16" t="s">
         <v>0</v>
       </c>
-      <c r="Q16" t="s">
-        <v>0</v>
+      <c r="Q16">
+        <v>560000</v>
       </c>
       <c r="R16" t="s">
         <v>0</v>
@@ -1957,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
         <v>0</v>
@@ -1969,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
         <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
       </c>
       <c r="J17" t="s">
         <v>0</v>
@@ -2049,7 +2055,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
         <v>0</v>
@@ -2061,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
@@ -2070,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
         <v>0</v>
@@ -2509,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
         <v>0</v>
@@ -2598,7 +2604,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>0</v>
@@ -2690,7 +2696,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
@@ -2720,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
         <v>0</v>
